--- a/documentation/keywords.xlsx
+++ b/documentation/keywords.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="description." localSheetId="0">'par-file'!$A$1:$B$202</definedName>
     <definedName name="options_values." localSheetId="0">'par-file'!$C$1:$C$202</definedName>
-    <definedName name="order." localSheetId="0">'par-file'!$F$1:$F$212</definedName>
+    <definedName name="order." localSheetId="0">'par-file'!$G$1:$G$212</definedName>
     <definedName name="recommended." localSheetId="0">'par-file'!$E$4:$E$202</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="317">
   <si>
     <t xml:space="preserve">RestartFile    </t>
   </si>
@@ -770,9 +770,6 @@
     <t>A comment is defined  by a leading Hashtag (#). Valid whitespaces are 'tab' 'carriage-return' and 'space'</t>
   </si>
   <si>
-    <t>Residence time</t>
-  </si>
-  <si>
     <t>lorentz-berthelot-factor</t>
   </si>
   <si>
@@ -933,9 +930,6 @@
   </si>
   <si>
     <t>100</t>
-  </si>
-  <si>
-    <t>Gear</t>
   </si>
   <si>
     <t>~1</t>
@@ -1047,6 +1041,12 @@
       </rPr>
       <t/>
     </r>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>units</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1256,19 +1256,19 @@
     <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1283,13 +1283,19 @@
     <xf numFmtId="49" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1612,39 +1618,42 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="72.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="40.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="1"/>
+    <col min="5" max="6" width="9.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="23" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>235</v>
       </c>
@@ -1653,26 +1662,29 @@
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
       <c r="F2" s="28"/>
-    </row>
-    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="28"/>
+    </row>
+    <row r="3" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1682,11 +1694,12 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -1697,38 +1710,41 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>223</v>
       </c>
@@ -1737,16 +1753,18 @@
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="30"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="30"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
         <v>230</v>
       </c>
@@ -1755,8 +1773,9 @@
       <c r="D11" s="29"/>
       <c r="E11" s="29"/>
       <c r="F11" s="29"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="29"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>6</v>
       </c>
@@ -1770,11 +1789,12 @@
       <c r="E12" s="5">
         <v>201600</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="5"/>
+      <c r="G12" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>8</v>
       </c>
@@ -1788,11 +1808,12 @@
       <c r="E13" s="5">
         <v>60</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>10</v>
       </c>
@@ -1803,14 +1824,15 @@
         <v>185</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="5">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>12</v>
       </c>
@@ -1824,11 +1846,12 @@
       <c r="E15" s="5">
         <v>3.5</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>14</v>
       </c>
@@ -1842,11 +1865,12 @@
       <c r="E16" s="5">
         <v>100</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>16</v>
       </c>
@@ -1860,11 +1884,12 @@
       <c r="E17" s="5">
         <v>40</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>18</v>
       </c>
@@ -1876,11 +1901,12 @@
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="5">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>20</v>
       </c>
@@ -1890,27 +1916,29 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="5">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="5">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>23</v>
       </c>
@@ -1918,19 +1946,20 @@
         <v>24</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>291</v>
+        <v>194</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
         <v>224</v>
       </c>
@@ -1939,8 +1968,9 @@
       <c r="D22" s="29"/>
       <c r="E22" s="29"/>
       <c r="F22" s="29"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="29"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>25</v>
       </c>
@@ -1949,16 +1979,17 @@
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E23" s="5">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>27</v>
       </c>
@@ -1972,11 +2003,12 @@
       <c r="E24" s="5">
         <v>0.5</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="5"/>
+      <c r="G24" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>29</v>
       </c>
@@ -1985,16 +2017,17 @@
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E25" s="5">
         <v>0</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>31</v>
       </c>
@@ -2006,11 +2039,12 @@
       <c r="E26" s="5">
         <v>0</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="5"/>
+      <c r="G26" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
         <v>33</v>
       </c>
@@ -2019,16 +2053,17 @@
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E27" s="5">
         <v>0</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="5"/>
+      <c r="G27" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>35</v>
       </c>
@@ -2037,16 +2072,17 @@
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E28" s="5">
         <v>0</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="5"/>
+      <c r="G28" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
         <v>37</v>
       </c>
@@ -2058,11 +2094,12 @@
       <c r="E29" s="5">
         <v>0</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="5"/>
+      <c r="G29" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
@@ -2074,11 +2111,12 @@
       <c r="E30" s="5">
         <v>0</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="5"/>
+      <c r="G30" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
@@ -2090,11 +2128,12 @@
       <c r="E31" s="5">
         <v>0</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="5"/>
+      <c r="G31" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>43</v>
       </c>
@@ -2105,16 +2144,17 @@
         <v>187</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E32" s="5">
         <v>0</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="5"/>
+      <c r="G32" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>45</v>
       </c>
@@ -2125,16 +2165,17 @@
         <v>188</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="5"/>
+      <c r="G33" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>47</v>
       </c>
@@ -2143,16 +2184,17 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E34" s="5">
         <v>0</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="5"/>
+      <c r="G34" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>49</v>
       </c>
@@ -2161,16 +2203,17 @@
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E35" s="5">
         <v>0</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="5"/>
+      <c r="G35" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
         <v>222</v>
       </c>
@@ -2179,8 +2222,9 @@
       <c r="D36" s="29"/>
       <c r="E36" s="29"/>
       <c r="F36" s="29"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" s="29"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>51</v>
       </c>
@@ -2189,16 +2233,17 @@
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E37" s="5">
         <v>0</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="5"/>
+      <c r="G37" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>53</v>
       </c>
@@ -2207,16 +2252,17 @@
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E38" s="5">
         <v>200</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="5"/>
+      <c r="G38" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>55</v>
       </c>
@@ -2228,11 +2274,12 @@
       <c r="E39" s="5">
         <v>500</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="5"/>
+      <c r="G39" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>56</v>
       </c>
@@ -2244,11 +2291,12 @@
       <c r="E40" s="5">
         <v>41868</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="5"/>
+      <c r="G40" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
         <v>220</v>
       </c>
@@ -2257,26 +2305,28 @@
       <c r="D41" s="29"/>
       <c r="E41" s="29"/>
       <c r="F41" s="29"/>
-    </row>
-    <row r="42" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G41" s="29"/>
+    </row>
+    <row r="42" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>58</v>
       </c>
@@ -2284,19 +2334,20 @@
         <v>59</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="5"/>
+      <c r="G43" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>60</v>
       </c>
@@ -2304,11 +2355,12 @@
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
-      <c r="F44" s="16">
+      <c r="F44" s="16"/>
+      <c r="G44" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
         <v>61</v>
       </c>
@@ -2316,11 +2368,12 @@
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
-      <c r="F45" s="16">
+      <c r="F45" s="16"/>
+      <c r="G45" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
         <v>62</v>
       </c>
@@ -2328,11 +2381,12 @@
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
-      <c r="F46" s="16">
+      <c r="F46" s="16"/>
+      <c r="G46" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
         <v>63</v>
       </c>
@@ -2340,11 +2394,12 @@
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
-      <c r="F47" s="16">
+      <c r="F47" s="16"/>
+      <c r="G47" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>64</v>
       </c>
@@ -2352,11 +2407,12 @@
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
-      <c r="F48" s="16">
+      <c r="F48" s="16"/>
+      <c r="G48" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
         <v>65</v>
       </c>
@@ -2364,11 +2420,12 @@
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
-      <c r="F49" s="16">
+      <c r="F49" s="16"/>
+      <c r="G49" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
         <v>66</v>
       </c>
@@ -2376,11 +2433,12 @@
       <c r="C50" s="16"/>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
-      <c r="F50" s="16">
+      <c r="F50" s="16"/>
+      <c r="G50" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="29" t="s">
         <v>221</v>
       </c>
@@ -2389,64 +2447,69 @@
       <c r="D51" s="29"/>
       <c r="E51" s="29"/>
       <c r="F51" s="29"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51" s="29"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
-      <c r="F52" s="5">
+      <c r="F52" s="5"/>
+      <c r="G52" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
-      <c r="F53" s="5">
+      <c r="F53" s="5"/>
+      <c r="G53" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
-      <c r="F54" s="5">
+      <c r="F54" s="5"/>
+      <c r="G54" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
-      <c r="F55" s="5">
+      <c r="F55" s="5"/>
+      <c r="G55" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="31" t="s">
         <v>225</v>
       </c>
@@ -2455,26 +2518,29 @@
       <c r="D56" s="31"/>
       <c r="E56" s="31"/>
       <c r="F56" s="31"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G56" s="31"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="31"/>
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
       <c r="D57" s="31"/>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="24" t="s">
+      <c r="G57" s="31"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
         <v>71</v>
       </c>
@@ -2483,30 +2549,32 @@
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="24"/>
+      <c r="G59" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="21" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F60" s="24"/>
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
         <v>72</v>
       </c>
@@ -2516,11 +2584,12 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="4">
+      <c r="F61" s="24"/>
+      <c r="G61" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="22" t="s">
         <v>74</v>
       </c>
@@ -2530,11 +2599,12 @@
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
-      <c r="F62" s="4">
+      <c r="F62" s="24"/>
+      <c r="G62" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
         <v>76</v>
       </c>
@@ -2544,11 +2614,12 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="4">
+      <c r="F63" s="24"/>
+      <c r="G63" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="21" t="s">
         <v>78</v>
       </c>
@@ -2558,21 +2629,23 @@
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
-      <c r="F64" s="4">
+      <c r="F64" s="24"/>
+      <c r="G64" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="24" t="s">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>80</v>
       </c>
@@ -2582,11 +2655,12 @@
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-      <c r="F66" s="4">
+      <c r="F66" s="24"/>
+      <c r="G66" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="21" t="s">
         <v>82</v>
       </c>
@@ -2596,11 +2670,12 @@
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="4">
+      <c r="F67" s="24"/>
+      <c r="G67" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="21" t="s">
         <v>84</v>
       </c>
@@ -2608,11 +2683,12 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
-      <c r="F68" s="4">
+      <c r="F68" s="24"/>
+      <c r="G68" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
         <v>85</v>
       </c>
@@ -2620,11 +2696,12 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="4">
+      <c r="F69" s="24"/>
+      <c r="G69" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="21" t="s">
         <v>86</v>
       </c>
@@ -2632,11 +2709,12 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="4">
+      <c r="F70" s="24"/>
+      <c r="G70" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="21" t="s">
         <v>87</v>
       </c>
@@ -2644,11 +2722,12 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="4">
+      <c r="F71" s="24"/>
+      <c r="G71" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="21" t="s">
         <v>88</v>
       </c>
@@ -2656,11 +2735,12 @@
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="4">
+      <c r="F72" s="24"/>
+      <c r="G72" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="21" t="s">
         <v>89</v>
       </c>
@@ -2668,11 +2748,12 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="4">
+      <c r="F73" s="24"/>
+      <c r="G73" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="21" t="s">
         <v>90</v>
       </c>
@@ -2680,21 +2761,23 @@
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
-      <c r="F74" s="4">
+      <c r="F74" s="24"/>
+      <c r="G74" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="B75" s="27"/>
+      <c r="C75" s="27"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
         <v>91</v>
       </c>
@@ -2704,11 +2787,12 @@
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
-      <c r="F76" s="4">
+      <c r="F76" s="24"/>
+      <c r="G76" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
         <v>93</v>
       </c>
@@ -2717,14 +2801,15 @@
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E77" s="4"/>
-      <c r="F77" s="4">
+      <c r="F77" s="24"/>
+      <c r="G77" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="21" t="s">
         <v>95</v>
       </c>
@@ -2738,11 +2823,12 @@
       <c r="E78" s="4">
         <v>1</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F78" s="24"/>
+      <c r="G78" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="21" t="s">
         <v>97</v>
       </c>
@@ -2752,11 +2838,12 @@
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="4">
+      <c r="F79" s="24"/>
+      <c r="G79" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="21" t="s">
         <v>98</v>
       </c>
@@ -2766,16 +2853,17 @@
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="4">
+      <c r="F80" s="24"/>
+      <c r="G80" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="21" t="s">
         <v>175</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>190</v>
@@ -2784,11 +2872,12 @@
       <c r="E81" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F81" s="24"/>
+      <c r="G81" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="21" t="s">
         <v>176</v>
       </c>
@@ -2796,19 +2885,21 @@
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="B83" s="24"/>
-      <c r="C83" s="24"/>
-      <c r="D83" s="24"/>
-      <c r="E83" s="24"/>
-      <c r="F83" s="24"/>
-    </row>
-    <row r="84" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="F82" s="24"/>
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="B83" s="27"/>
+      <c r="C83" s="27"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+    </row>
+    <row r="84" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>99</v>
       </c>
@@ -2822,11 +2913,12 @@
       <c r="E84" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="17"/>
+      <c r="G84" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>100</v>
       </c>
@@ -2838,11 +2930,12 @@
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="17"/>
-      <c r="F85" s="4">
+      <c r="F85" s="17"/>
+      <c r="G85" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>102</v>
       </c>
@@ -2854,11 +2947,12 @@
       <c r="E86" s="17">
         <v>0</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="17"/>
+      <c r="G86" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>174</v>
       </c>
@@ -2866,9 +2960,10 @@
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-    </row>
-    <row r="88" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F87" s="24"/>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>103</v>
       </c>
@@ -2879,12 +2974,13 @@
         <v>215</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F88" s="24"/>
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>104</v>
       </c>
@@ -2894,9 +2990,10 @@
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F89" s="24"/>
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>105</v>
       </c>
@@ -2906,9 +3003,10 @@
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F90" s="24"/>
+      <c r="G90" s="4"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>106</v>
       </c>
@@ -2918,9 +3016,10 @@
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F91" s="24"/>
+      <c r="G91" s="4"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>107</v>
       </c>
@@ -2930,9 +3029,10 @@
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F92" s="24"/>
+      <c r="G92" s="4"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>108</v>
       </c>
@@ -2942,9 +3042,10 @@
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F93" s="24"/>
+      <c r="G93" s="4"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>109</v>
       </c>
@@ -2954,9 +3055,10 @@
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F94" s="24"/>
+      <c r="G94" s="4"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>110</v>
       </c>
@@ -2966,43 +3068,47 @@
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F95" s="24"/>
+      <c r="G95" s="4"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="B96" s="26" t="s">
-        <v>286</v>
+      <c r="B96" s="32" t="s">
+        <v>285</v>
       </c>
       <c r="C96" s="18"/>
       <c r="D96" s="18"/>
       <c r="E96" s="18"/>
-      <c r="F96" s="18"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F96" s="24"/>
+      <c r="G96" s="18"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="B97" s="26"/>
+      <c r="B97" s="32"/>
       <c r="C97" s="18"/>
       <c r="D97" s="18"/>
       <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F97" s="24"/>
+      <c r="G97" s="18"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="18" t="s">
         <v>123</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C98" s="18"/>
       <c r="D98" s="18"/>
       <c r="E98" s="18"/>
-      <c r="F98" s="18"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F98" s="24"/>
+      <c r="G98" s="18"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="18" t="s">
         <v>124</v>
       </c>
@@ -3010,9 +3116,10 @@
       <c r="C99" s="18"/>
       <c r="D99" s="18"/>
       <c r="E99" s="18"/>
-      <c r="F99" s="18"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F99" s="24"/>
+      <c r="G99" s="18"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="18" t="s">
         <v>125</v>
       </c>
@@ -3020,9 +3127,10 @@
       <c r="C100" s="18"/>
       <c r="D100" s="18"/>
       <c r="E100" s="18"/>
-      <c r="F100" s="18"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F100" s="24"/>
+      <c r="G100" s="18"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="18" t="s">
         <v>126</v>
       </c>
@@ -3030,9 +3138,10 @@
       <c r="C101" s="18"/>
       <c r="D101" s="18"/>
       <c r="E101" s="18"/>
-      <c r="F101" s="18"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F101" s="24"/>
+      <c r="G101" s="18"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="18" t="s">
         <v>127</v>
       </c>
@@ -3040,9 +3149,10 @@
       <c r="C102" s="18"/>
       <c r="D102" s="18"/>
       <c r="E102" s="18"/>
-      <c r="F102" s="18"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F102" s="24"/>
+      <c r="G102" s="18"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="18" t="s">
         <v>128</v>
       </c>
@@ -3050,121 +3160,131 @@
       <c r="C103" s="18"/>
       <c r="D103" s="18"/>
       <c r="E103" s="18"/>
-      <c r="F103" s="18"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="B104" s="24"/>
-      <c r="C104" s="24"/>
-      <c r="D104" s="24"/>
-      <c r="E104" s="24"/>
-      <c r="F104" s="24"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F103" s="24"/>
+      <c r="G103" s="18"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="B104" s="27"/>
+      <c r="C104" s="27"/>
+      <c r="D104" s="27"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="27"/>
+      <c r="G104" s="27"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="21" t="s">
         <v>227</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F105" s="24"/>
+      <c r="G105" s="4"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="21" t="s">
         <v>111</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F106" s="24"/>
+      <c r="G106" s="4"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="21" t="s">
         <v>112</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-    </row>
-    <row r="108" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F107" s="24"/>
+      <c r="G107" s="4"/>
+    </row>
+    <row r="108" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="21" t="s">
         <v>113</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F108" s="24"/>
+      <c r="G108" s="4"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="21" t="s">
         <v>114</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
-      <c r="F109" s="4"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F109" s="24"/>
+      <c r="G109" s="4"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="21" t="s">
         <v>115</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F110" s="24"/>
+      <c r="G110" s="4"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="21" t="s">
         <v>116</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E111" s="4"/>
-      <c r="F111" s="4"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F111" s="24"/>
+      <c r="G111" s="4"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="21" t="s">
         <v>117</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F112" s="24"/>
+      <c r="G112" s="4"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>118</v>
       </c>
@@ -3172,9 +3292,10 @@
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F113" s="24"/>
+      <c r="G113" s="4"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>119</v>
       </c>
@@ -3182,9 +3303,10 @@
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
-      <c r="F114" s="4"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F114" s="24"/>
+      <c r="G114" s="4"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>120</v>
       </c>
@@ -3192,19 +3314,21 @@
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
-      <c r="F115" s="4"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="24" t="s">
+      <c r="F115" s="24"/>
+      <c r="G115" s="4"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="B116" s="24"/>
-      <c r="C116" s="24"/>
-      <c r="D116" s="24"/>
-      <c r="E116" s="24"/>
-      <c r="F116" s="24"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="27"/>
+      <c r="C116" s="27"/>
+      <c r="D116" s="27"/>
+      <c r="E116" s="27"/>
+      <c r="F116" s="27"/>
+      <c r="G116" s="27"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>129</v>
       </c>
@@ -3212,9 +3336,10 @@
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
-      <c r="F117" s="4"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F117" s="24"/>
+      <c r="G117" s="4"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>130</v>
       </c>
@@ -3222,9 +3347,10 @@
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
-      <c r="F118" s="4"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F118" s="24"/>
+      <c r="G118" s="4"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>131</v>
       </c>
@@ -3232,9 +3358,10 @@
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
-      <c r="F119" s="4"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F119" s="24"/>
+      <c r="G119" s="4"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>132</v>
       </c>
@@ -3242,9 +3369,10 @@
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
-      <c r="F120" s="4"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F120" s="24"/>
+      <c r="G120" s="4"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>133</v>
       </c>
@@ -3252,9 +3380,10 @@
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F121" s="24"/>
+      <c r="G121" s="4"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>134</v>
       </c>
@@ -3262,9 +3391,10 @@
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
-      <c r="F122" s="4"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F122" s="24"/>
+      <c r="G122" s="4"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>135</v>
       </c>
@@ -3272,9 +3402,10 @@
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
-      <c r="F123" s="4"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F123" s="24"/>
+      <c r="G123" s="4"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>136</v>
       </c>
@@ -3282,9 +3413,10 @@
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
-      <c r="F124" s="4"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F124" s="24"/>
+      <c r="G124" s="4"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="21" t="s">
         <v>137</v>
       </c>
@@ -3292,9 +3424,10 @@
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
-      <c r="F125" s="4"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F125" s="24"/>
+      <c r="G125" s="4"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="21" t="s">
         <v>138</v>
       </c>
@@ -3302,9 +3435,10 @@
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
-      <c r="F126" s="4"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F126" s="24"/>
+      <c r="G126" s="4"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="21" t="s">
         <v>139</v>
       </c>
@@ -3312,9 +3446,10 @@
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F127" s="24"/>
+      <c r="G127" s="4"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="21" t="s">
         <v>140</v>
       </c>
@@ -3322,9 +3457,10 @@
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
-      <c r="F128" s="4"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F128" s="24"/>
+      <c r="G128" s="4"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="21" t="s">
         <v>141</v>
       </c>
@@ -3332,19 +3468,21 @@
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
-      <c r="F129" s="4"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="B130" s="23"/>
-      <c r="C130" s="23"/>
-      <c r="D130" s="23"/>
-      <c r="E130" s="23"/>
-      <c r="F130" s="23"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F129" s="24"/>
+      <c r="G129" s="4"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B130" s="26"/>
+      <c r="C130" s="26"/>
+      <c r="D130" s="26"/>
+      <c r="E130" s="26"/>
+      <c r="F130" s="26"/>
+      <c r="G130" s="26"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>177</v>
       </c>
@@ -3352,9 +3490,10 @@
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F131" s="25"/>
+      <c r="G131" s="3"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>178</v>
       </c>
@@ -3362,9 +3501,10 @@
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F132" s="25"/>
+      <c r="G132" s="3"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>179</v>
       </c>
@@ -3372,9 +3512,10 @@
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F133" s="25"/>
+      <c r="G133" s="3"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>180</v>
       </c>
@@ -3382,9 +3523,10 @@
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F134" s="25"/>
+      <c r="G134" s="3"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>181</v>
       </c>
@@ -3392,9 +3534,10 @@
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F135" s="25"/>
+      <c r="G135" s="3"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>182</v>
       </c>
@@ -3402,9 +3545,10 @@
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
-      <c r="F136" s="3"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F136" s="25"/>
+      <c r="G136" s="3"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>183</v>
       </c>
@@ -3412,9 +3556,10 @@
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
-      <c r="F137" s="3"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F137" s="25"/>
+      <c r="G137" s="3"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>184</v>
       </c>
@@ -3422,9 +3567,10 @@
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
-      <c r="F138" s="3"/>
-    </row>
-    <row r="139" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F138" s="25"/>
+      <c r="G138" s="3"/>
+    </row>
+    <row r="139" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>101</v>
       </c>
@@ -3436,29 +3582,30 @@
         <v>2</v>
       </c>
       <c r="E139" s="17"/>
-      <c r="F139" s="4">
+      <c r="F139" s="17"/>
+      <c r="G139" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A130:G130"/>
+    <mergeCell ref="A104:G104"/>
+    <mergeCell ref="A116:G116"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A9:G10"/>
+    <mergeCell ref="A56:G57"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="B96:B97"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A3:F4"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="A56:F57"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A130:F130"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A3:G4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="portrait" horizontalDpi="4294967294" verticalDpi="4294967294" r:id="rId1"/>
@@ -3506,7 +3653,7 @@
         <v>192</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>217</v>
@@ -3516,36 +3663,36 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -3556,10 +3703,10 @@
         <v>144</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -3569,7 +3716,7 @@
         <v>146</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -3581,26 +3728,26 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>154</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -3610,8 +3757,8 @@
       <c r="A11" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>271</v>
+      <c r="B11" s="36" t="s">
+        <v>270</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -3621,7 +3768,7 @@
       <c r="A12" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -3630,7 +3777,7 @@
       <c r="A13" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="33"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -3640,7 +3787,7 @@
         <v>158</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -3651,7 +3798,7 @@
         <v>159</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -3662,20 +3809,20 @@
         <v>160</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -3741,13 +3888,13 @@
       <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="34" t="s">
         <v>233</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
@@ -3831,13 +3978,13 @@
       <c r="E34" s="9"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
@@ -3921,13 +4068,13 @@
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
+      <c r="A45" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
@@ -3966,20 +4113,20 @@
       <c r="E49" s="9"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -3990,10 +4137,10 @@
         <v>145</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -4003,27 +4150,27 @@
         <v>147</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
+      <c r="A54" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -4031,10 +4178,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -4045,27 +4192,27 @@
         <v>168</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="32" t="s">
-        <v>284</v>
-      </c>
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
+      <c r="A58" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="B58" s="34"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -4076,7 +4223,7 @@
         <v>169</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
@@ -4087,24 +4234,24 @@
         <v>168</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="3"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
+      <c r="A62" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -4131,7 +4278,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -4140,7 +4287,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -4175,13 +4322,13 @@
       <c r="E70" s="9"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
+      <c r="A71" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
@@ -4203,7 +4350,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
